--- a/01_Thermal/B_results/four_gp_analysis.xlsx
+++ b/01_Thermal/B_results/four_gp_analysis.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="four_gp_analysis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="four_gp_core_strength" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,19 +484,19 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>88.97330548645829</v>
+        <v>82.3610154268341</v>
       </c>
       <c r="E2" t="n">
-        <v>192.1862854350307</v>
+        <v>151.4627808616233</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3839322388138813</v>
+        <v>0.7437672650641654</v>
       </c>
       <c r="G2" t="n">
-        <v>766.0799590426855</v>
+        <v>2356.862560923433</v>
       </c>
       <c r="H2" t="n">
-        <v>5197.146252046272</v>
+        <v>4260.495759386248</v>
       </c>
     </row>
     <row r="3">
@@ -511,19 +512,19 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>48.78291496058195</v>
+        <v>43.49704858819949</v>
       </c>
       <c r="E3" t="n">
-        <v>41.5219361933559</v>
+        <v>27.27905384269594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1426047271259213</v>
+        <v>0.3019739350912453</v>
       </c>
       <c r="G3" t="n">
-        <v>202.5690122257402</v>
+        <v>502.7105425383907</v>
       </c>
       <c r="H3" t="n">
-        <v>9961.051064780582</v>
+        <v>5512.886817461289</v>
       </c>
     </row>
     <row r="4">
@@ -539,19 +540,19 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>44.68142181986482</v>
+        <v>46.15619797910912</v>
       </c>
       <c r="E4" t="n">
-        <v>31.25011493488006</v>
+        <v>34.20950549112766</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2101293375391492</v>
+        <v>0.3525871326530648</v>
       </c>
       <c r="G4" t="n">
-        <v>239.5906346755411</v>
+        <v>468.2667972631416</v>
       </c>
       <c r="H4" t="n">
-        <v>5426.208224240896</v>
+        <v>3766.694924158668</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +568,19 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>42.26384050529389</v>
+        <v>46.20849645094592</v>
       </c>
       <c r="E5" t="n">
-        <v>26.96878861254851</v>
+        <v>34.5450388236128</v>
       </c>
       <c r="F5" t="n">
-        <v>0.213325491522378</v>
+        <v>0.4490009889836231</v>
       </c>
       <c r="G5" t="n">
-        <v>1462.266641379961</v>
+        <v>3454.541139170676</v>
       </c>
       <c r="H5" t="n">
-        <v>32132.24447896824</v>
+        <v>17135.46024586531</v>
       </c>
     </row>
     <row r="6">
@@ -595,19 +596,19 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>32.21218949645617</v>
+        <v>36.1888636456892</v>
       </c>
       <c r="E6" t="n">
-        <v>15.06754796279567</v>
+        <v>18.07053957724579</v>
       </c>
       <c r="F6" t="n">
-        <v>0.145143247872032</v>
+        <v>0.2606419671301973</v>
       </c>
       <c r="G6" t="n">
-        <v>371.7263098869855</v>
+        <v>485.7815754575333</v>
       </c>
       <c r="H6" t="n">
-        <v>17645.32355961575</v>
+        <v>7150.76242849565</v>
       </c>
     </row>
     <row r="7">
@@ -623,19 +624,19 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>19.9747437953366</v>
+        <v>25.18401080940476</v>
       </c>
       <c r="E7" t="n">
-        <v>3.931068103128829</v>
+        <v>6.084365335227245</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1375529660427273</v>
+        <v>0.1769583646469677</v>
       </c>
       <c r="G7" t="n">
-        <v>140.0327074938703</v>
+        <v>213.1441002097149</v>
       </c>
       <c r="H7" t="n">
-        <v>7400.985730980938</v>
+        <v>6806.614016268456</v>
       </c>
     </row>
     <row r="8">
@@ -651,19 +652,19 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>15.54934309754688</v>
+        <v>21.39883950820372</v>
       </c>
       <c r="E8" t="n">
-        <v>2.513860733708374</v>
+        <v>4.229069733610023</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09344800909330855</v>
+        <v>0.1396883634895008</v>
       </c>
       <c r="G8" t="n">
-        <v>64.25128543908592</v>
+        <v>99.47126567398068</v>
       </c>
       <c r="H8" t="n">
-        <v>7357.69387224937</v>
+        <v>5097.734174531417</v>
       </c>
     </row>
     <row r="9">
@@ -672,24 +673,1431 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>292.4377591615386</v>
+        <v>300.9944724083863</v>
       </c>
       <c r="E9" t="n">
-        <v>313.4396019754481</v>
+        <v>275.8803536651428</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1952950954691891</v>
+        <v>0.3904314809687011</v>
       </c>
       <c r="G9" t="n">
-        <v>3246.51655014387</v>
+        <v>7580.777981236869</v>
       </c>
       <c r="H9" t="n">
-        <v>85120.65318288203</v>
+        <v>49730.64836616704</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>z_m</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>outlet_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>outlet_x_m</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>outlet_y_m</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>core_radius_m</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>n_core_samples</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>core_strength_obs_mps</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>core_strength_pred_mps</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>core_mean_obs_mps</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>core_mean_pred_mps</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>z020</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.069319438289516</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.5775</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.519164226240398</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>z020</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.804184824880667</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.343333333333333</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.917666010683945</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>z020</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.318225439783094</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.205974701300385</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>z020</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.283</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.511673993465381</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.354333333333334</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.643999648434219</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>z020</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>27.083</v>
+      </c>
+      <c r="I6" t="n">
+        <v>14.70340369641866</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.77075</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.675850924104665</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>z035</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.672</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.076356308543625</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.5935</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.457679344218884</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>z035</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.598</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.586767247603831</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.582</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.74611518050025</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>z035</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.346</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.07148840949587</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.14975</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.042460908616317</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>z035</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.606</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.430277073715315</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.422666666666667</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.502210153258759</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>z035</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>16.222</v>
+      </c>
+      <c r="I11" t="n">
+        <v>14.16488903935864</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.0555</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.54122225983966</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>z050</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.322</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.034816536747871</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.951</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.365242687277541</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>z050</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.283561933842808</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.944333333333333</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.525614557873404</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>z050</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.389</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.680700157784131</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.5625</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.816481288103938</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>z050</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.734</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.281945018639145</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.32637953274339</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>z050</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="I16" t="n">
+        <v>13.28102364701396</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.320255911753489</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>z075</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.997</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.869961044686688</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.188220459286101</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>z075</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.182</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.749340202790621</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.721</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.143163946824858</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>z075</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.611</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.918929659951921</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.375669368733002</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>z075</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.509</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.959399456274559</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.03295348578966</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>z075</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12.299</v>
+      </c>
+      <c r="I21" t="n">
+        <v>11.49763036370379</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.07475</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.874407590925947</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>z110</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.954</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.486172333062758</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.02725</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.944296087428091</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>z110</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.144</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.115739352259915</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.503666666666667</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.696453662352122</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>z110</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.044879505631144</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.25525</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.760459722974638</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>z110</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.317</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.409864335172299</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.458</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.684501698546401</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>z110</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>14</v>
+      </c>
+      <c r="H26" t="n">
+        <v>9.057</v>
+      </c>
+      <c r="I26" t="n">
+        <v>9.056655526126116</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.26425</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.264163881531529</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>z160</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.598</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.322641700660616</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.5755</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.595673085326525</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>z160</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.464</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.408053709687203</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.202666666666667</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.249682121025246</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>z160</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.402</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.463568085657081</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.1765</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.164625542615104</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>z160</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.042</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.663872614071543</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.508666666666667</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.333001357081127</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>z160</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G31" t="n">
+        <v>14</v>
+      </c>
+      <c r="H31" t="n">
+        <v>7.505999999999999</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6.858136110076443</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.8765</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.714534027519111</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>z220</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.037788857963845</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.196</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.240221098917486</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>z220</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.303415924612118</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.8406666666666668</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.9102236278293806</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>z220</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.294024728680098</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.7117500000000001</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.7969854721765385</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>z220</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.458</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.366098032443793</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.9506666666666668</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.987365504326907</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>z220</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G36" t="n">
+        <v>14</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6.886</v>
+      </c>
+      <c r="I36" t="n">
+        <v>6.001327543699853</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.7215</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.500331885924963</v>
       </c>
     </row>
   </sheetData>

--- a/01_Thermal/B_results/four_gp_analysis.xlsx
+++ b/01_Thermal/B_results/four_gp_analysis.xlsx
@@ -484,19 +484,19 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>82.3610154268341</v>
+        <v>81.31086870473465</v>
       </c>
       <c r="E2" t="n">
-        <v>151.4627808616233</v>
+        <v>144.0978574067872</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7437672650641654</v>
+        <v>0.7610908959117698</v>
       </c>
       <c r="G2" t="n">
-        <v>2356.862560923433</v>
+        <v>2551.177434455447</v>
       </c>
       <c r="H2" t="n">
-        <v>4260.495759386248</v>
+        <v>4404.205864527997</v>
       </c>
     </row>
     <row r="3">
@@ -512,19 +512,19 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>43.49704858819949</v>
+        <v>42.19575715209965</v>
       </c>
       <c r="E3" t="n">
-        <v>27.27905384269594</v>
+        <v>23.84260657928462</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3019739350912453</v>
+        <v>0.2851432705807638</v>
       </c>
       <c r="G3" t="n">
-        <v>502.7105425383907</v>
+        <v>599.7821573679723</v>
       </c>
       <c r="H3" t="n">
-        <v>5512.886817461289</v>
+        <v>7376.787765444902</v>
       </c>
     </row>
     <row r="4">
@@ -540,19 +540,19 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>46.15619797910912</v>
+        <v>46.48584643045524</v>
       </c>
       <c r="E4" t="n">
-        <v>34.20950549112766</v>
+        <v>35.17258691684101</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3525871326530648</v>
+        <v>0.3757971900913929</v>
       </c>
       <c r="G4" t="n">
-        <v>468.2667972631416</v>
+        <v>472.386039256942</v>
       </c>
       <c r="H4" t="n">
-        <v>3766.694924158668</v>
+        <v>3344.952825335054</v>
       </c>
     </row>
     <row r="5">
@@ -568,19 +568,19 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>46.20849645094592</v>
+        <v>46.54460845232605</v>
       </c>
       <c r="E5" t="n">
-        <v>34.5450388236128</v>
+        <v>34.27788223580475</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4490009889836231</v>
+        <v>0.3518962866366952</v>
       </c>
       <c r="G5" t="n">
-        <v>3454.541139170676</v>
+        <v>3853.768073775997</v>
       </c>
       <c r="H5" t="n">
-        <v>17135.46024586531</v>
+        <v>31121.19082608325</v>
       </c>
     </row>
     <row r="6">
@@ -596,19 +596,19 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>36.1888636456892</v>
+        <v>36.10516087301351</v>
       </c>
       <c r="E6" t="n">
-        <v>18.07053957724579</v>
+        <v>17.8989000059161</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2606419671301973</v>
+        <v>0.2505076428757969</v>
       </c>
       <c r="G6" t="n">
-        <v>485.7815754575333</v>
+        <v>490.2566134727456</v>
       </c>
       <c r="H6" t="n">
-        <v>7150.76242849565</v>
+        <v>7812.346546992781</v>
       </c>
     </row>
     <row r="7">
@@ -624,19 +624,19 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>25.18401080940476</v>
+        <v>25.06529381981143</v>
       </c>
       <c r="E7" t="n">
-        <v>6.084365335227245</v>
+        <v>6.074947891054626</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1769583646469677</v>
+        <v>0.1769303764684793</v>
       </c>
       <c r="G7" t="n">
-        <v>213.1441002097149</v>
+        <v>218.5579919151729</v>
       </c>
       <c r="H7" t="n">
-        <v>6806.614016268456</v>
+        <v>6981.71133541129</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>21.39883950820372</v>
+        <v>20.89858193380744</v>
       </c>
       <c r="E8" t="n">
-        <v>4.229069733610023</v>
+        <v>4.013109287935976</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1396883634895008</v>
+        <v>0.1312248920163647</v>
       </c>
       <c r="G8" t="n">
-        <v>99.47126567398068</v>
+        <v>120.0472342836361</v>
       </c>
       <c r="H8" t="n">
-        <v>5097.734174531417</v>
+        <v>6971.395325081485</v>
       </c>
     </row>
     <row r="9">
@@ -677,19 +677,19 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>300.9944724083863</v>
+        <v>298.606117366248</v>
       </c>
       <c r="E9" t="n">
-        <v>275.8803536651428</v>
+        <v>265.3778903236243</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3904314809687011</v>
+        <v>0.3494625693699507</v>
       </c>
       <c r="G9" t="n">
-        <v>7580.777981236869</v>
+        <v>8305.975544527913</v>
       </c>
       <c r="H9" t="n">
-        <v>49730.64836616704</v>
+        <v>68012.59048887675</v>
       </c>
     </row>
   </sheetData>
@@ -793,13 +793,13 @@
         <v>7.31</v>
       </c>
       <c r="I2" t="n">
-        <v>3.069319438289516</v>
+        <v>3.168266804809539</v>
       </c>
       <c r="J2" t="n">
         <v>4.5775</v>
       </c>
       <c r="K2" t="n">
-        <v>2.519164226240398</v>
+        <v>2.537543740906221</v>
       </c>
     </row>
     <row r="3">
@@ -832,13 +832,13 @@
         <v>6.66</v>
       </c>
       <c r="I3" t="n">
-        <v>3.804184824880667</v>
+        <v>3.815956378665958</v>
       </c>
       <c r="J3" t="n">
         <v>4.343333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>2.917666010683945</v>
+        <v>2.915645519882922</v>
       </c>
     </row>
     <row r="4">
@@ -871,13 +871,13 @@
         <v>6.83</v>
       </c>
       <c r="I4" t="n">
-        <v>4.318225439783094</v>
+        <v>4.355175061822238</v>
       </c>
       <c r="J4" t="n">
         <v>4.58</v>
       </c>
       <c r="K4" t="n">
-        <v>3.205974701300385</v>
+        <v>3.215320214330773</v>
       </c>
     </row>
     <row r="5">
@@ -910,13 +910,13 @@
         <v>6.283</v>
       </c>
       <c r="I5" t="n">
-        <v>3.511673993465381</v>
+        <v>3.632646815923727</v>
       </c>
       <c r="J5" t="n">
         <v>4.354333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>2.643999648434219</v>
+        <v>2.636647061557163</v>
       </c>
     </row>
     <row r="6">
@@ -945,13 +945,13 @@
         <v>27.083</v>
       </c>
       <c r="I6" t="n">
-        <v>14.70340369641866</v>
+        <v>14.97204506122146</v>
       </c>
       <c r="J6" t="n">
         <v>6.77075</v>
       </c>
       <c r="K6" t="n">
-        <v>3.675850924104665</v>
+        <v>3.743011265305365</v>
       </c>
     </row>
     <row r="7">
@@ -984,13 +984,13 @@
         <v>3.672</v>
       </c>
       <c r="I7" t="n">
-        <v>3.076356308543625</v>
+        <v>3.173178621248191</v>
       </c>
       <c r="J7" t="n">
         <v>2.5935</v>
       </c>
       <c r="K7" t="n">
-        <v>2.457679344218884</v>
+        <v>2.47452887289442</v>
       </c>
     </row>
     <row r="8">
@@ -1023,13 +1023,13 @@
         <v>3.598</v>
       </c>
       <c r="I8" t="n">
-        <v>3.586767247603831</v>
+        <v>3.594517651356861</v>
       </c>
       <c r="J8" t="n">
         <v>2.582</v>
       </c>
       <c r="K8" t="n">
-        <v>2.74611518050025</v>
+        <v>2.743084997519317</v>
       </c>
     </row>
     <row r="9">
@@ -1062,13 +1062,13 @@
         <v>5.346</v>
       </c>
       <c r="I9" t="n">
-        <v>4.07148840949587</v>
+        <v>4.09949825106343</v>
       </c>
       <c r="J9" t="n">
         <v>3.14975</v>
       </c>
       <c r="K9" t="n">
-        <v>3.042460908616317</v>
+        <v>3.050197769767539</v>
       </c>
     </row>
     <row r="10">
@@ -1101,13 +1101,13 @@
         <v>3.606</v>
       </c>
       <c r="I10" t="n">
-        <v>3.430277073715315</v>
+        <v>3.538630961022178</v>
       </c>
       <c r="J10" t="n">
         <v>2.422666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>2.502210153258759</v>
+        <v>2.491267126321043</v>
       </c>
     </row>
     <row r="11">
@@ -1136,13 +1136,13 @@
         <v>16.222</v>
       </c>
       <c r="I11" t="n">
-        <v>14.16488903935864</v>
+        <v>14.40582548469066</v>
       </c>
       <c r="J11" t="n">
         <v>4.0555</v>
       </c>
       <c r="K11" t="n">
-        <v>3.54122225983966</v>
+        <v>3.601456371172665</v>
       </c>
     </row>
     <row r="12">
@@ -1175,13 +1175,13 @@
         <v>3.322</v>
       </c>
       <c r="I12" t="n">
-        <v>3.034816536747871</v>
+        <v>3.12095287281501</v>
       </c>
       <c r="J12" t="n">
         <v>1.951</v>
       </c>
       <c r="K12" t="n">
-        <v>2.365242687277541</v>
+        <v>2.378219592249311</v>
       </c>
     </row>
     <row r="13">
@@ -1214,13 +1214,13 @@
         <v>2.395</v>
       </c>
       <c r="I13" t="n">
-        <v>3.283561933842808</v>
+        <v>3.285488633164511</v>
       </c>
       <c r="J13" t="n">
         <v>1.944333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>2.525614557873404</v>
+        <v>2.520148613557926</v>
       </c>
     </row>
     <row r="14">
@@ -1253,13 +1253,13 @@
         <v>3.389</v>
       </c>
       <c r="I14" t="n">
-        <v>3.680700157784131</v>
+        <v>3.695934542456939</v>
       </c>
       <c r="J14" t="n">
         <v>2.5625</v>
       </c>
       <c r="K14" t="n">
-        <v>2.816481288103938</v>
+        <v>2.820963270125649</v>
       </c>
     </row>
     <row r="15">
@@ -1292,13 +1292,13 @@
         <v>2.734</v>
       </c>
       <c r="I15" t="n">
-        <v>3.281945018639145</v>
+        <v>3.370748871750047</v>
       </c>
       <c r="J15" t="n">
         <v>1.724</v>
       </c>
       <c r="K15" t="n">
-        <v>2.32637953274339</v>
+        <v>2.313619549304641</v>
       </c>
     </row>
     <row r="16">
@@ -1327,13 +1327,13 @@
         <v>11.84</v>
       </c>
       <c r="I16" t="n">
-        <v>13.28102364701396</v>
+        <v>13.47312492018651</v>
       </c>
       <c r="J16" t="n">
         <v>2.96</v>
       </c>
       <c r="K16" t="n">
-        <v>3.320255911753489</v>
+        <v>3.368281230046627</v>
       </c>
     </row>
     <row r="17">
@@ -1366,13 +1366,13 @@
         <v>2.997</v>
       </c>
       <c r="I17" t="n">
-        <v>2.869961044686688</v>
+        <v>2.92984794856881</v>
       </c>
       <c r="J17" t="n">
         <v>1.869</v>
       </c>
       <c r="K17" t="n">
-        <v>2.188220459286101</v>
+        <v>2.19435210904364</v>
       </c>
     </row>
     <row r="18">
@@ -1405,13 +1405,13 @@
         <v>2.182</v>
       </c>
       <c r="I18" t="n">
-        <v>2.749340202790621</v>
+        <v>2.744694508334748</v>
       </c>
       <c r="J18" t="n">
         <v>1.721</v>
       </c>
       <c r="K18" t="n">
-        <v>2.143163946824858</v>
+        <v>2.134632227309754</v>
       </c>
     </row>
     <row r="19">
@@ -1444,13 +1444,13 @@
         <v>3.611</v>
       </c>
       <c r="I19" t="n">
-        <v>2.918929659951921</v>
+        <v>2.914028814397063</v>
       </c>
       <c r="J19" t="n">
         <v>2.48</v>
       </c>
       <c r="K19" t="n">
-        <v>2.375669368733002</v>
+        <v>2.37446296309883</v>
       </c>
     </row>
     <row r="20">
@@ -1483,13 +1483,13 @@
         <v>3.509</v>
       </c>
       <c r="I20" t="n">
-        <v>2.959399456274559</v>
+        <v>3.017542315889257</v>
       </c>
       <c r="J20" t="n">
         <v>1.865</v>
       </c>
       <c r="K20" t="n">
-        <v>2.03295348578966</v>
+        <v>2.021809854495111</v>
       </c>
     </row>
     <row r="21">
@@ -1518,13 +1518,13 @@
         <v>12.299</v>
       </c>
       <c r="I21" t="n">
-        <v>11.49763036370379</v>
+        <v>11.60611358718988</v>
       </c>
       <c r="J21" t="n">
         <v>3.07475</v>
       </c>
       <c r="K21" t="n">
-        <v>2.874407590925947</v>
+        <v>2.901528396797469</v>
       </c>
     </row>
     <row r="22">
@@ -1557,13 +1557,13 @@
         <v>2.954</v>
       </c>
       <c r="I22" t="n">
-        <v>2.486172333062758</v>
+        <v>2.512337196838422</v>
       </c>
       <c r="J22" t="n">
         <v>2.02725</v>
       </c>
       <c r="K22" t="n">
-        <v>1.944296087428091</v>
+        <v>1.944614857094842</v>
       </c>
     </row>
     <row r="23">
@@ -1596,13 +1596,13 @@
         <v>2.144</v>
       </c>
       <c r="I23" t="n">
-        <v>2.115739352259915</v>
+        <v>2.109953869474775</v>
       </c>
       <c r="J23" t="n">
         <v>1.503666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>1.696453662352122</v>
+        <v>1.68795393455295</v>
       </c>
     </row>
     <row r="24">
@@ -1635,13 +1635,13 @@
         <v>1.642</v>
       </c>
       <c r="I24" t="n">
-        <v>2.044879505631144</v>
+        <v>2.027148910098978</v>
       </c>
       <c r="J24" t="n">
         <v>1.25525</v>
       </c>
       <c r="K24" t="n">
-        <v>1.760459722974638</v>
+        <v>1.753820565042944</v>
       </c>
     </row>
     <row r="25">
@@ -1674,13 +1674,13 @@
         <v>2.317</v>
       </c>
       <c r="I25" t="n">
-        <v>2.409864335172299</v>
+        <v>2.434493567412171</v>
       </c>
       <c r="J25" t="n">
         <v>1.458</v>
       </c>
       <c r="K25" t="n">
-        <v>1.684501698546401</v>
+        <v>1.67778827159527</v>
       </c>
     </row>
     <row r="26">
@@ -1709,13 +1709,13 @@
         <v>9.057</v>
       </c>
       <c r="I26" t="n">
-        <v>9.056655526126116</v>
+        <v>9.083933543824347</v>
       </c>
       <c r="J26" t="n">
         <v>2.26425</v>
       </c>
       <c r="K26" t="n">
-        <v>2.264163881531529</v>
+        <v>2.270983385956087</v>
       </c>
     </row>
     <row r="27">
@@ -1748,13 +1748,13 @@
         <v>2.598</v>
       </c>
       <c r="I27" t="n">
-        <v>2.322641700660616</v>
+        <v>2.327218825984067</v>
       </c>
       <c r="J27" t="n">
         <v>1.5755</v>
       </c>
       <c r="K27" t="n">
-        <v>1.595673085326525</v>
+        <v>1.592250540189885</v>
       </c>
     </row>
     <row r="28">
@@ -1787,13 +1787,13 @@
         <v>1.464</v>
       </c>
       <c r="I28" t="n">
-        <v>1.408053709687203</v>
+        <v>1.40342803785005</v>
       </c>
       <c r="J28" t="n">
         <v>1.202666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>1.249682121025246</v>
+        <v>1.245431105901221</v>
       </c>
     </row>
     <row r="29">
@@ -1826,13 +1826,13 @@
         <v>1.402</v>
       </c>
       <c r="I29" t="n">
-        <v>1.463568085657081</v>
+        <v>1.452866321594004</v>
       </c>
       <c r="J29" t="n">
         <v>1.1765</v>
       </c>
       <c r="K29" t="n">
-        <v>1.164625542615104</v>
+        <v>1.160397537256141</v>
       </c>
     </row>
     <row r="30">
@@ -1865,13 +1865,13 @@
         <v>2.042</v>
       </c>
       <c r="I30" t="n">
-        <v>1.663872614071543</v>
+        <v>1.666961858333106</v>
       </c>
       <c r="J30" t="n">
         <v>1.508666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>1.333001357081127</v>
+        <v>1.333514125537942</v>
       </c>
     </row>
     <row r="31">
@@ -1900,13 +1900,13 @@
         <v>7.505999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>6.858136110076443</v>
+        <v>6.850475043761227</v>
       </c>
       <c r="J31" t="n">
         <v>1.8765</v>
       </c>
       <c r="K31" t="n">
-        <v>1.714534027519111</v>
+        <v>1.712618760940307</v>
       </c>
     </row>
     <row r="32">
@@ -1939,13 +1939,13 @@
         <v>2.347</v>
       </c>
       <c r="I32" t="n">
-        <v>2.037788857963845</v>
+        <v>2.042173311212675</v>
       </c>
       <c r="J32" t="n">
         <v>1.196</v>
       </c>
       <c r="K32" t="n">
-        <v>1.240221098917486</v>
+        <v>1.235282989539084</v>
       </c>
     </row>
     <row r="33">
@@ -1978,13 +1978,13 @@
         <v>1.6</v>
       </c>
       <c r="I33" t="n">
-        <v>1.303415924612118</v>
+        <v>1.310452220095766</v>
       </c>
       <c r="J33" t="n">
         <v>0.8406666666666668</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9102236278293806</v>
+        <v>0.9108613720370293</v>
       </c>
     </row>
     <row r="34">
@@ -2017,13 +2017,13 @@
         <v>1.481</v>
       </c>
       <c r="I34" t="n">
-        <v>1.294024728680098</v>
+        <v>1.296622113493214</v>
       </c>
       <c r="J34" t="n">
         <v>0.7117500000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7969854721765385</v>
+        <v>0.7988634213176041</v>
       </c>
     </row>
     <row r="35">
@@ -2056,13 +2056,13 @@
         <v>1.458</v>
       </c>
       <c r="I35" t="n">
-        <v>1.366098032443793</v>
+        <v>1.373034485072174</v>
       </c>
       <c r="J35" t="n">
         <v>0.9506666666666668</v>
       </c>
       <c r="K35" t="n">
-        <v>0.987365504326907</v>
+        <v>0.9894815233772033</v>
       </c>
     </row>
     <row r="36">
@@ -2091,13 +2091,13 @@
         <v>6.886</v>
       </c>
       <c r="I36" t="n">
-        <v>6.001327543699853</v>
+        <v>6.022282129873829</v>
       </c>
       <c r="J36" t="n">
         <v>1.7215</v>
       </c>
       <c r="K36" t="n">
-        <v>1.500331885924963</v>
+        <v>1.505570532468457</v>
       </c>
     </row>
   </sheetData>
